--- a/nvi_etl/survey/conf/cdo_workbook_template.xlsx
+++ b/nvi_etl/survey/conf/cdo_workbook_template.xlsx
@@ -1,59 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\2_responsibilities\nvi_etl\nvi_etl\survey\conf\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3852D5DF-5138-4665-807E-D35002867A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="About" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>About:</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptable Use: </t>
+  </si>
+  <si>
+    <t>This workbook contains a special cut of the Neighborhood Vitality Index Data for the {cdo_name} Neighborhood.  The dataset includes primary data collected from residents via the Neighborhood Vitality Index Survey during {year}.  Please note that this dataset is still in its developmental stage and is not necessarily a representative sample.</t>
+  </si>
+  <si>
+    <t>This data cut is strictly designated for internal use by {cdo_name} authorized personnel. Access to this data is limited to employees, contractors, and partners explicitly authorized by {cdo_name}. All information within the data cut is considered confidential and proprietary to {cdo_name}, requiring users to maintain its confidentiality and refrain from disclosing it externally without prior written consent. Users are responsible for ensuring the security and integrity of the data, including safeguarding against unauthorized access and utilizing secure methods for storage and transmission. Unauthorized activities such as data sharing with external entities or modification without proper authorization are strictly prohibited. By accessing the data cut, users agree to comply with all applicable laws, regulations, and organizational policies, and acknowledge their responsibility to adhere to the outlined terms and conditions.</t>
+  </si>
+  <si>
+    <t>Neighborhood Vitality Index {year}; Data Driven Detroit, {survey_year_plus_one}</t>
+  </si>
+  <si>
+    <t>Neighborhood Vitality Index Data, {year}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
       <name val="IBM Plex Sans"/>
-      <color rgb="00999999"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="IBM Plex Sans"/>
-      <b val="1"/>
-      <sz val="16"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="IBM Plex Sans"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="IBM Plex Sans"/>
-      <sz val="10"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="IBM Plex Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="IBM Plex Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -61,93 +112,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3400424" cy="1085242"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D208E6E-0B37-4B9B-8FE1-F703A7D716E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="0"/>
+          <a:ext cx="3400424" cy="1085242"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,88 +576,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="60.85546875" customWidth="1"/>
+    <col min="2" max="2" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="80" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>{logo}</t>
-        </is>
+    <row r="1" spans="1:2" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>{cdo_name} — NVI Community Survey {year}</t>
-        </is>
+    <row r="2" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>About This Report</t>
-        </is>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>{about_text}</t>
-        </is>
+    <row r="3" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Methodology</t>
-        </is>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>{methodology_text}</t>
-        </is>
+    <row r="4" spans="1:2" ht="205.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>2</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Data Suppression</t>
-        </is>
+      <c r="B4" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>{suppression_text}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>{contact_text}</t>
-        </is>
-      </c>
+    <row r="5" spans="1:2" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>